--- a/output/Test_Cases_collection/TC01 - Successful Login.xlsx
+++ b/output/Test_Cases_collection/TC01 - Successful Login.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="26">
   <si>
     <t>Test Case Name</t>
   </si>
@@ -52,18 +52,24 @@
     <t>3</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>Launch the application and open `https://www.saucedemo.com/`.</t>
   </si>
   <si>
-    <t>Enter `standard_user` in the "user-name" field.</t>
-  </si>
-  <si>
-    <t>Enter `secret_sauce` in the "password" field.</t>
+    <t>Enter "standard_user" in the "user-name" field.</t>
+  </si>
+  <si>
+    <t>Enter "secret_sauce" in the "password" field.</t>
   </si>
   <si>
     <t>Click on "login-button".</t>
   </si>
   <si>
+    <t>Verify the inventory page is displayed with product listings.</t>
+  </si>
+  <si>
     <t>The login page is displayed with username and password fields.</t>
   </si>
   <si>
@@ -73,7 +79,10 @@
     <t>The password is entered successfully.</t>
   </si>
   <si>
-    <t>The user is redirected to the inventory page.</t>
+    <t>The user is redirected to the inventory page (`https://www.saucedemo.com/inventory.html`).</t>
+  </si>
+  <si>
+    <t>The inventory page is displayed with product details and "Add to Cart" buttons.</t>
   </si>
   <si>
     <t>New</t>
@@ -440,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -474,19 +483,19 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -497,16 +506,16 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -517,16 +526,16 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -537,16 +546,36 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F5" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/output/Test_Cases_collection/TC01 - Successful Login.xlsx
+++ b/output/Test_Cases_collection/TC01 - Successful Login.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="29">
   <si>
     <t>Test Case Name</t>
   </si>
@@ -55,34 +55,43 @@
     <t>4</t>
   </si>
   <si>
-    <t>Launch the application and open `https://www.saucedemo.com/`.</t>
-  </si>
-  <si>
-    <t>Enter "standard_user" in the "user-name" field.</t>
-  </si>
-  <si>
-    <t>Enter "secret_sauce" in the "password" field.</t>
-  </si>
-  <si>
-    <t>Click on "login-button".</t>
-  </si>
-  <si>
-    <t>Verify the inventory page is displayed with product listings.</t>
-  </si>
-  <si>
-    <t>The login page is displayed with username and password fields.</t>
-  </si>
-  <si>
-    <t>The username is entered successfully.</t>
-  </si>
-  <si>
-    <t>The password is entered successfully.</t>
-  </si>
-  <si>
-    <t>The user is redirected to the inventory page (`https://www.saucedemo.com/inventory.html`).</t>
-  </si>
-  <si>
-    <t>The inventory page is displayed with product details and "Add to Cart" buttons.</t>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Launch the application and open `https://mindful-shark-fv3y29-dev-ed.trailblaze.lightning.force.com/`</t>
+  </si>
+  <si>
+    <t>Enter "rajaram111294@mindful-shark-fv3y29.com" in the "Username" field</t>
+  </si>
+  <si>
+    <t>Enter "[PASSWORD]" in the "Password" field</t>
+  </si>
+  <si>
+    <t>Click on "Log In"</t>
+  </si>
+  <si>
+    <t>Enter "[VERIFICATION_CODE]" in the "Verification Code" field</t>
+  </si>
+  <si>
+    <t>Click on "Verify"</t>
+  </si>
+  <si>
+    <t>Salesforce login page is displayed.</t>
+  </si>
+  <si>
+    <t>Username is entered successfully.</t>
+  </si>
+  <si>
+    <t>Password is entered successfully.</t>
+  </si>
+  <si>
+    <t>User is redirected to the verification page.</t>
+  </si>
+  <si>
+    <t>Verification code is entered successfully.</t>
+  </si>
+  <si>
+    <t>User is redirected to the Salesforce Home page.</t>
   </si>
   <si>
     <t>New</t>
@@ -449,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -483,19 +492,19 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -506,16 +515,16 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -526,16 +535,16 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -546,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -566,16 +575,36 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F6" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
